--- a/resources/HEARTH_Shot_List_Template.xlsx
+++ b/resources/HEARTH_Shot_List_Template.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="129">
   <si>
     <t xml:space="preserve">HEARTH  ·  Short Film Shot List</t>
   </si>
@@ -240,6 +240,9 @@
   </si>
   <si>
     <t xml:space="preserve">SCENE ___  —  INT / EXT  —  LOCATION  —  TIME OF DAY  (fill in)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HEARTH  ·  Production Resource Library  ·  buildyourhearth.studio</t>
   </si>
   <si>
     <t xml:space="preserve">HEARTH  ·  Shot Type Quick Reference</t>
@@ -414,7 +417,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -471,6 +474,14 @@
     <font>
       <sz val="10"/>
       <color rgb="FF0D1B2E"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="8"/>
+      <color rgb="FF888898"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -597,11 +608,15 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -646,7 +661,11 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -658,11 +677,11 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -696,7 +715,7 @@
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FFCDC8BE"/>
-      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF888898"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFF5F0E8"/>
@@ -922,621 +941,638 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:L34"/>
+  <dimension ref="A1:L36"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="5" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="5" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="2" t="s">
+      <c r="C4" s="4"/>
+      <c r="D4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="2" t="s">
+      <c r="E4" s="4"/>
+      <c r="F4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="2" t="s">
+      <c r="G4" s="4"/>
+      <c r="H4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="2" t="s">
+      <c r="I4" s="4"/>
+      <c r="J4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K4" s="3"/>
+      <c r="K4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="6" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="J6" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="K6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="L6" s="4" t="s">
+      <c r="L6" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="H8" s="6" t="s">
+      <c r="H8" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="I8" s="6" t="s">
+      <c r="I8" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="J8" s="6" t="s">
+      <c r="J8" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="K8" s="7" t="s">
+      <c r="K8" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="L8" s="7" t="s">
+      <c r="L8" s="8" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="I9" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="J9" s="8" t="s">
+      <c r="J9" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="K9" s="9" t="s">
+      <c r="K9" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="L9" s="9" t="s">
+      <c r="L9" s="10" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="H10" s="6" t="s">
+      <c r="H10" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="I10" s="6" t="s">
+      <c r="I10" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="J10" s="6" t="s">
+      <c r="J10" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="K10" s="7" t="s">
+      <c r="K10" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="L10" s="7" t="s">
+      <c r="L10" s="8" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="E11" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="G11" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="H11" s="8" t="s">
+      <c r="H11" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="I11" s="8" t="s">
+      <c r="I11" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="J11" s="8" t="s">
+      <c r="J11" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="K11" s="9" t="s">
+      <c r="K11" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="L11" s="9" t="s">
+      <c r="L11" s="10" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="G12" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="H12" s="6" t="s">
+      <c r="H12" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="I12" s="6" t="s">
+      <c r="I12" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="J12" s="6" t="s">
+      <c r="J12" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="K12" s="7" t="s">
+      <c r="K12" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="L12" s="7" t="s">
+      <c r="L12" s="8" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="6"/>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="E15" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="F15" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="G15" s="8" t="s">
+      <c r="G15" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="H15" s="8" t="s">
+      <c r="H15" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="I15" s="8" t="s">
+      <c r="I15" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="J15" s="8" t="s">
+      <c r="J15" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="K15" s="9" t="s">
+      <c r="K15" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="L15" s="9" t="s">
+      <c r="L15" s="10" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="F16" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="G16" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="6" t="s">
+      <c r="H16" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="I16" s="6" t="s">
+      <c r="I16" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="J16" s="6" t="s">
+      <c r="J16" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="K16" s="7" t="s">
+      <c r="K16" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="L16" s="7" t="s">
+      <c r="L16" s="8" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="E17" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="F17" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="G17" s="8" t="s">
+      <c r="G17" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="H17" s="8" t="s">
+      <c r="H17" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="I17" s="8" t="s">
+      <c r="I17" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="J17" s="8" t="s">
+      <c r="J17" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="K17" s="9" t="s">
+      <c r="K17" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="L17" s="9" t="s">
+      <c r="L17" s="10" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="5"/>
-      <c r="K19" s="5"/>
-      <c r="L19" s="5"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6"/>
+      <c r="K19" s="6"/>
+      <c r="L19" s="6"/>
     </row>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="10"/>
-      <c r="K20" s="11"/>
-      <c r="L20" s="11"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="12"/>
+      <c r="L20" s="12"/>
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
-      <c r="I21" s="10"/>
-      <c r="J21" s="10"/>
-      <c r="K21" s="11"/>
-      <c r="L21" s="11"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="12"/>
+      <c r="L21" s="12"/>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="10"/>
-      <c r="K22" s="11"/>
-      <c r="L22" s="11"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="12"/>
+      <c r="L22" s="12"/>
     </row>
     <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="10"/>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10"/>
-      <c r="I23" s="10"/>
-      <c r="J23" s="10"/>
-      <c r="K23" s="11"/>
-      <c r="L23" s="11"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="11"/>
+      <c r="K23" s="12"/>
+      <c r="L23" s="12"/>
     </row>
     <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="10"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="10"/>
-      <c r="I24" s="10"/>
-      <c r="J24" s="10"/>
-      <c r="K24" s="11"/>
-      <c r="L24" s="11"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
+      <c r="J24" s="11"/>
+      <c r="K24" s="12"/>
+      <c r="L24" s="12"/>
     </row>
     <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="10"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="10"/>
-      <c r="I25" s="10"/>
-      <c r="J25" s="10"/>
-      <c r="K25" s="11"/>
-      <c r="L25" s="11"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="11"/>
+      <c r="K25" s="12"/>
+      <c r="L25" s="12"/>
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="10"/>
-      <c r="I26" s="10"/>
-      <c r="J26" s="10"/>
-      <c r="K26" s="11"/>
-      <c r="L26" s="11"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
+      <c r="J26" s="11"/>
+      <c r="K26" s="12"/>
+      <c r="L26" s="12"/>
     </row>
     <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="10"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="10"/>
-      <c r="I27" s="10"/>
-      <c r="J27" s="10"/>
-      <c r="K27" s="11"/>
-      <c r="L27" s="11"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="11"/>
+      <c r="J27" s="11"/>
+      <c r="K27" s="12"/>
+      <c r="L27" s="12"/>
     </row>
     <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="10"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="11"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="10"/>
-      <c r="I28" s="10"/>
-      <c r="J28" s="10"/>
-      <c r="K28" s="11"/>
-      <c r="L28" s="11"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="11"/>
+      <c r="J28" s="11"/>
+      <c r="K28" s="12"/>
+      <c r="L28" s="12"/>
     </row>
     <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="10"/>
-      <c r="C29" s="10"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="11"/>
-      <c r="F29" s="10"/>
-      <c r="G29" s="10"/>
-      <c r="H29" s="10"/>
-      <c r="I29" s="10"/>
-      <c r="J29" s="10"/>
-      <c r="K29" s="11"/>
-      <c r="L29" s="11"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="12"/>
+      <c r="L29" s="12"/>
     </row>
     <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="10"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="11"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="10"/>
-      <c r="H30" s="10"/>
-      <c r="I30" s="10"/>
-      <c r="J30" s="10"/>
-      <c r="K30" s="11"/>
-      <c r="L30" s="11"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11"/>
+      <c r="J30" s="11"/>
+      <c r="K30" s="12"/>
+      <c r="L30" s="12"/>
     </row>
     <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="10"/>
-      <c r="C31" s="10"/>
-      <c r="D31" s="10"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="10"/>
-      <c r="G31" s="10"/>
-      <c r="H31" s="10"/>
-      <c r="I31" s="10"/>
-      <c r="J31" s="10"/>
-      <c r="K31" s="11"/>
-      <c r="L31" s="11"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="11"/>
+      <c r="J31" s="11"/>
+      <c r="K31" s="12"/>
+      <c r="L31" s="12"/>
     </row>
     <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="10"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="10"/>
-      <c r="G32" s="10"/>
-      <c r="H32" s="10"/>
-      <c r="I32" s="10"/>
-      <c r="J32" s="10"/>
-      <c r="K32" s="11"/>
-      <c r="L32" s="11"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="11"/>
+      <c r="J32" s="11"/>
+      <c r="K32" s="12"/>
+      <c r="L32" s="12"/>
     </row>
     <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="10"/>
-      <c r="C33" s="10"/>
-      <c r="D33" s="10"/>
-      <c r="E33" s="11"/>
-      <c r="F33" s="10"/>
-      <c r="G33" s="10"/>
-      <c r="H33" s="10"/>
-      <c r="I33" s="10"/>
-      <c r="J33" s="10"/>
-      <c r="K33" s="11"/>
-      <c r="L33" s="11"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
+      <c r="J33" s="11"/>
+      <c r="K33" s="12"/>
+      <c r="L33" s="12"/>
     </row>
     <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="10"/>
-      <c r="C34" s="10"/>
-      <c r="D34" s="10"/>
-      <c r="E34" s="11"/>
-      <c r="F34" s="10"/>
-      <c r="G34" s="10"/>
-      <c r="H34" s="10"/>
-      <c r="I34" s="10"/>
-      <c r="J34" s="10"/>
-      <c r="K34" s="11"/>
-      <c r="L34" s="11"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="11"/>
+      <c r="J34" s="11"/>
+      <c r="K34" s="12"/>
+      <c r="L34" s="12"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="B36" s="13"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="13"/>
+      <c r="H36" s="13"/>
+      <c r="I36" s="13"/>
+      <c r="J36" s="13"/>
+      <c r="K36" s="13"/>
+      <c r="L36" s="13"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="B2:L2"/>
     <mergeCell ref="B7:L7"/>
     <mergeCell ref="B14:L14"/>
     <mergeCell ref="B19:L19"/>
+    <mergeCell ref="A36:L36"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1556,262 +1592,262 @@
   <dimension ref="B1:C36"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="50"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="3"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="C2" s="12"/>
+      <c r="B2" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" s="14"/>
     </row>
     <row r="3" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="C4" s="13"/>
+      <c r="B4" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4" s="15"/>
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="C5" s="15" t="s">
+      <c r="B5" s="16" t="s">
         <v>76</v>
       </c>
+      <c r="C5" s="17" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C6" s="16" t="s">
+      <c r="B6" s="3" t="s">
         <v>78</v>
       </c>
+      <c r="C6" s="18" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="C7" s="15" t="s">
+      <c r="B7" s="16" t="s">
         <v>80</v>
       </c>
+      <c r="C7" s="17" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C8" s="16" t="s">
+      <c r="B8" s="3" t="s">
         <v>82</v>
       </c>
+      <c r="C8" s="18" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="C9" s="15" t="s">
+      <c r="B9" s="16" t="s">
         <v>84</v>
       </c>
+      <c r="C9" s="17" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C10" s="16" t="s">
+      <c r="B10" s="3" t="s">
         <v>86</v>
       </c>
+      <c r="C10" s="18" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="C11" s="15" t="s">
+      <c r="B11" s="16" t="s">
         <v>88</v>
       </c>
+      <c r="C11" s="17" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C12" s="16" t="s">
+      <c r="B12" s="3" t="s">
         <v>90</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="C14" s="5"/>
+      <c r="B14" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C14" s="6"/>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="C15" s="15" t="s">
-        <v>92</v>
+      <c r="C15" s="17" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C16" s="16" t="s">
+      <c r="B16" s="3" t="s">
         <v>94</v>
       </c>
+      <c r="C16" s="18" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="C17" s="15" t="s">
+      <c r="B17" s="16" t="s">
         <v>96</v>
       </c>
+      <c r="C17" s="17" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C18" s="16" t="s">
+      <c r="B18" s="3" t="s">
         <v>98</v>
       </c>
+      <c r="C18" s="18" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="C19" s="15" t="s">
+      <c r="B19" s="16" t="s">
         <v>100</v>
       </c>
+      <c r="C19" s="17" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C20" s="16" t="s">
-        <v>101</v>
+      <c r="C20" s="18" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="14" t="s">
+      <c r="B21" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="C21" s="15" t="s">
-        <v>102</v>
+      <c r="C21" s="17" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C22" s="16" t="s">
+      <c r="B22" s="3" t="s">
         <v>104</v>
       </c>
+      <c r="C22" s="18" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="C23" s="15" t="s">
+      <c r="B23" s="16" t="s">
         <v>106</v>
       </c>
+      <c r="C23" s="17" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C24" s="16" t="s">
+      <c r="B24" s="3" t="s">
         <v>108</v>
+      </c>
+      <c r="C24" s="18" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="C26" s="17"/>
+      <c r="B26" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="C26" s="19"/>
     </row>
     <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="14" t="s">
+      <c r="B27" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="C27" s="15" t="s">
-        <v>110</v>
+      <c r="C27" s="17" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C28" s="16" t="s">
-        <v>111</v>
+      <c r="C28" s="18" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="C29" s="15" t="s">
+      <c r="B29" s="16" t="s">
         <v>113</v>
       </c>
+      <c r="C29" s="17" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C30" s="16" t="s">
+      <c r="B30" s="3" t="s">
         <v>115</v>
       </c>
+      <c r="C30" s="18" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="C31" s="15" t="s">
+      <c r="B31" s="16" t="s">
         <v>117</v>
       </c>
+      <c r="C31" s="17" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C32" s="16" t="s">
+      <c r="B32" s="3" t="s">
         <v>119</v>
       </c>
+      <c r="C32" s="18" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="C33" s="15" t="s">
+      <c r="B33" s="16" t="s">
         <v>121</v>
       </c>
+      <c r="C33" s="17" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C34" s="16" t="s">
+      <c r="B34" s="3" t="s">
         <v>123</v>
       </c>
+      <c r="C34" s="18" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="C35" s="15" t="s">
+      <c r="B35" s="16" t="s">
         <v>125</v>
       </c>
+      <c r="C35" s="17" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="C36" s="16" t="s">
+      <c r="B36" s="3" t="s">
         <v>127</v>
+      </c>
+      <c r="C36" s="18" t="s">
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/resources/HEARTH_Shot_List_Template.xlsx
+++ b/resources/HEARTH_Shot_List_Template.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="128">
   <si>
     <t xml:space="preserve">HEARTH  ·  Short Film Shot List</t>
   </si>
@@ -240,9 +240,6 @@
   </si>
   <si>
     <t xml:space="preserve">SCENE ___  —  INT / EXT  —  LOCATION  —  TIME OF DAY  (fill in)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HEARTH  ·  Production Resource Library  ·  buildyourhearth.studio</t>
   </si>
   <si>
     <t xml:space="preserve">HEARTH  ·  Shot Type Quick Reference</t>
@@ -417,7 +414,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -474,14 +471,6 @@
     <font>
       <sz val="10"/>
       <color rgb="FF0D1B2E"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <i val="true"/>
-      <sz val="8"/>
-      <color rgb="FF888898"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -608,12 +597,8 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -661,11 +646,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -677,11 +658,11 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -715,7 +696,7 @@
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FFCDC8BE"/>
-      <rgbColor rgb="FF888898"/>
+      <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFF5F0E8"/>
@@ -941,638 +922,621 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L36"/>
+  <dimension ref="B1:L34"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="5" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="5" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="3" t="s">
+      <c r="C4" s="3"/>
+      <c r="D4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="3" t="s">
+      <c r="E4" s="3"/>
+      <c r="F4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="3" t="s">
+      <c r="G4" s="3"/>
+      <c r="H4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="I4" s="4"/>
-      <c r="J4" s="3" t="s">
+      <c r="I4" s="3"/>
+      <c r="J4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="K4" s="4"/>
+      <c r="K4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="6" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="I6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="J6" s="5" t="s">
+      <c r="J6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="K6" s="5" t="s">
+      <c r="K6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="L6" s="5" t="s">
+      <c r="L6" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="I8" s="7" t="s">
+      <c r="I8" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="J8" s="7" t="s">
+      <c r="J8" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="K8" s="8" t="s">
+      <c r="K8" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="L8" s="8" t="s">
+      <c r="L8" s="7" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="F9" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="G9" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="H9" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="I9" s="9" t="s">
+      <c r="I9" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="J9" s="9" t="s">
+      <c r="J9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="K9" s="10" t="s">
+      <c r="K9" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="L9" s="10" t="s">
+      <c r="L9" s="9" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="G10" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="H10" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="I10" s="7" t="s">
+      <c r="I10" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="J10" s="7" t="s">
+      <c r="J10" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="K10" s="8" t="s">
+      <c r="K10" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="L10" s="8" t="s">
+      <c r="L10" s="7" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="F11" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="G11" s="9" t="s">
+      <c r="G11" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="H11" s="9" t="s">
+      <c r="H11" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="I11" s="9" t="s">
+      <c r="I11" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="J11" s="9" t="s">
+      <c r="J11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="K11" s="10" t="s">
+      <c r="K11" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L11" s="10" t="s">
+      <c r="L11" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="G12" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="H12" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="I12" s="7" t="s">
+      <c r="I12" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="J12" s="7" t="s">
+      <c r="J12" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="K12" s="8" t="s">
+      <c r="K12" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="L12" s="8" t="s">
+      <c r="L12" s="7" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
-      <c r="L14" s="6"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E15" s="10" t="s">
+      <c r="E15" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="F15" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="G15" s="9" t="s">
+      <c r="G15" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="H15" s="9" t="s">
+      <c r="H15" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="I15" s="9" t="s">
+      <c r="I15" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="J15" s="9" t="s">
+      <c r="J15" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="K15" s="10" t="s">
+      <c r="K15" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="L15" s="10" t="s">
+      <c r="L15" s="9" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="E16" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="G16" s="7" t="s">
+      <c r="G16" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="7" t="s">
+      <c r="H16" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="I16" s="7" t="s">
+      <c r="I16" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="J16" s="7" t="s">
+      <c r="J16" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="K16" s="8" t="s">
+      <c r="K16" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="L16" s="8" t="s">
+      <c r="L16" s="7" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="D17" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E17" s="10" t="s">
+      <c r="E17" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="F17" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="G17" s="9" t="s">
+      <c r="G17" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="H17" s="9" t="s">
+      <c r="H17" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="I17" s="9" t="s">
+      <c r="I17" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="J17" s="9" t="s">
+      <c r="J17" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="K17" s="10" t="s">
+      <c r="K17" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="L17" s="10" t="s">
+      <c r="L17" s="9" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-      <c r="K19" s="6"/>
-      <c r="L19" s="6"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="5"/>
     </row>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="11"/>
-      <c r="J20" s="11"/>
-      <c r="K20" s="12"/>
-      <c r="L20" s="12"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="10"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="11"/>
+      <c r="L20" s="11"/>
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="11"/>
-      <c r="I21" s="11"/>
-      <c r="J21" s="11"/>
-      <c r="K21" s="12"/>
-      <c r="L21" s="12"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="10"/>
+      <c r="J21" s="10"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="11"/>
-      <c r="J22" s="11"/>
-      <c r="K22" s="12"/>
-      <c r="L22" s="12"/>
+      <c r="B22" s="10"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="10"/>
+      <c r="J22" s="10"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="11"/>
     </row>
     <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="11"/>
-      <c r="H23" s="11"/>
-      <c r="I23" s="11"/>
-      <c r="J23" s="11"/>
-      <c r="K23" s="12"/>
-      <c r="L23" s="12"/>
+      <c r="B23" s="10"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10"/>
+      <c r="I23" s="10"/>
+      <c r="J23" s="10"/>
+      <c r="K23" s="11"/>
+      <c r="L23" s="11"/>
     </row>
     <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="11"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="11"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11"/>
-      <c r="I24" s="11"/>
-      <c r="J24" s="11"/>
-      <c r="K24" s="12"/>
-      <c r="L24" s="12"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="10"/>
+      <c r="I24" s="10"/>
+      <c r="J24" s="10"/>
+      <c r="K24" s="11"/>
+      <c r="L24" s="11"/>
     </row>
     <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="11"/>
-      <c r="I25" s="11"/>
-      <c r="J25" s="11"/>
-      <c r="K25" s="12"/>
-      <c r="L25" s="12"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="10"/>
+      <c r="H25" s="10"/>
+      <c r="I25" s="10"/>
+      <c r="J25" s="10"/>
+      <c r="K25" s="11"/>
+      <c r="L25" s="11"/>
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="11"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="11"/>
-      <c r="I26" s="11"/>
-      <c r="J26" s="11"/>
-      <c r="K26" s="12"/>
-      <c r="L26" s="12"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="10"/>
+      <c r="H26" s="10"/>
+      <c r="I26" s="10"/>
+      <c r="J26" s="10"/>
+      <c r="K26" s="11"/>
+      <c r="L26" s="11"/>
     </row>
     <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="11"/>
-      <c r="I27" s="11"/>
-      <c r="J27" s="11"/>
-      <c r="K27" s="12"/>
-      <c r="L27" s="12"/>
+      <c r="B27" s="10"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="10"/>
+      <c r="G27" s="10"/>
+      <c r="H27" s="10"/>
+      <c r="I27" s="10"/>
+      <c r="J27" s="10"/>
+      <c r="K27" s="11"/>
+      <c r="L27" s="11"/>
     </row>
     <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="11"/>
-      <c r="C28" s="11"/>
-      <c r="D28" s="11"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="11"/>
-      <c r="H28" s="11"/>
-      <c r="I28" s="11"/>
-      <c r="J28" s="11"/>
-      <c r="K28" s="12"/>
-      <c r="L28" s="12"/>
+      <c r="B28" s="10"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="10"/>
+      <c r="I28" s="10"/>
+      <c r="J28" s="10"/>
+      <c r="K28" s="11"/>
+      <c r="L28" s="11"/>
     </row>
     <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="11"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="11"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="11"/>
-      <c r="H29" s="11"/>
-      <c r="I29" s="11"/>
-      <c r="J29" s="11"/>
-      <c r="K29" s="12"/>
-      <c r="L29" s="12"/>
+      <c r="B29" s="10"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="10"/>
+      <c r="H29" s="10"/>
+      <c r="I29" s="10"/>
+      <c r="J29" s="10"/>
+      <c r="K29" s="11"/>
+      <c r="L29" s="11"/>
     </row>
     <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="11"/>
-      <c r="C30" s="11"/>
-      <c r="D30" s="11"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="11"/>
-      <c r="H30" s="11"/>
-      <c r="I30" s="11"/>
-      <c r="J30" s="11"/>
-      <c r="K30" s="12"/>
-      <c r="L30" s="12"/>
+      <c r="B30" s="10"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="10"/>
+      <c r="G30" s="10"/>
+      <c r="H30" s="10"/>
+      <c r="I30" s="10"/>
+      <c r="J30" s="10"/>
+      <c r="K30" s="11"/>
+      <c r="L30" s="11"/>
     </row>
     <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="11"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="11"/>
-      <c r="H31" s="11"/>
-      <c r="I31" s="11"/>
-      <c r="J31" s="11"/>
-      <c r="K31" s="12"/>
-      <c r="L31" s="12"/>
+      <c r="B31" s="10"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="10"/>
+      <c r="G31" s="10"/>
+      <c r="H31" s="10"/>
+      <c r="I31" s="10"/>
+      <c r="J31" s="10"/>
+      <c r="K31" s="11"/>
+      <c r="L31" s="11"/>
     </row>
     <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="12"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="11"/>
-      <c r="H32" s="11"/>
-      <c r="I32" s="11"/>
-      <c r="J32" s="11"/>
-      <c r="K32" s="12"/>
-      <c r="L32" s="12"/>
+      <c r="B32" s="10"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="10"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="10"/>
+      <c r="G32" s="10"/>
+      <c r="H32" s="10"/>
+      <c r="I32" s="10"/>
+      <c r="J32" s="10"/>
+      <c r="K32" s="11"/>
+      <c r="L32" s="11"/>
     </row>
     <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="11"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="11"/>
-      <c r="G33" s="11"/>
-      <c r="H33" s="11"/>
-      <c r="I33" s="11"/>
-      <c r="J33" s="11"/>
-      <c r="K33" s="12"/>
-      <c r="L33" s="12"/>
+      <c r="B33" s="10"/>
+      <c r="C33" s="10"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="10"/>
+      <c r="G33" s="10"/>
+      <c r="H33" s="10"/>
+      <c r="I33" s="10"/>
+      <c r="J33" s="10"/>
+      <c r="K33" s="11"/>
+      <c r="L33" s="11"/>
     </row>
     <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="12"/>
-      <c r="F34" s="11"/>
-      <c r="G34" s="11"/>
-      <c r="H34" s="11"/>
-      <c r="I34" s="11"/>
-      <c r="J34" s="11"/>
-      <c r="K34" s="12"/>
-      <c r="L34" s="12"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="B36" s="13"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="13"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
-      <c r="G36" s="13"/>
-      <c r="H36" s="13"/>
-      <c r="I36" s="13"/>
-      <c r="J36" s="13"/>
-      <c r="K36" s="13"/>
-      <c r="L36" s="13"/>
+      <c r="B34" s="10"/>
+      <c r="C34" s="10"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="10"/>
+      <c r="G34" s="10"/>
+      <c r="H34" s="10"/>
+      <c r="I34" s="10"/>
+      <c r="J34" s="10"/>
+      <c r="K34" s="11"/>
+      <c r="L34" s="11"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="B2:L2"/>
     <mergeCell ref="B7:L7"/>
     <mergeCell ref="B14:L14"/>
     <mergeCell ref="B19:L19"/>
-    <mergeCell ref="A36:L36"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1592,262 +1556,262 @@
   <dimension ref="B1:C36"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="50"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="3"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="C2" s="14"/>
+      <c r="B2" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" s="12"/>
     </row>
     <row r="3" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="13"/>
+    </row>
+    <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="C4" s="15"/>
-    </row>
-    <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="16" t="s">
+      <c r="C5" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="C5" s="17" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="2" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="C6" s="18" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="14" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="16" t="s">
+      <c r="C7" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="C7" s="17" t="s">
+    </row>
+    <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="2" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="C8" s="18" t="s">
+    </row>
+    <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="14" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="16" t="s">
+      <c r="C9" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="C9" s="17" t="s">
+    </row>
+    <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="2" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="C10" s="18" t="s">
+    </row>
+    <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="14" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="16" t="s">
+      <c r="C11" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="C11" s="17" t="s">
+    </row>
+    <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="2" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="3" t="s">
+      <c r="C12" s="16" t="s">
         <v>90</v>
-      </c>
-      <c r="C12" s="18" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C14" s="5"/>
+    </row>
+    <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="C14" s="6"/>
-    </row>
-    <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="C15" s="17" t="s">
+    </row>
+    <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="2" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="3" t="s">
+      <c r="C16" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="C16" s="18" t="s">
+    </row>
+    <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="14" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="16" t="s">
+      <c r="C17" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C17" s="17" t="s">
+    </row>
+    <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="2" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="3" t="s">
+      <c r="C18" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="C18" s="18" t="s">
+    </row>
+    <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="14" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="16" t="s">
+      <c r="C19" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="C19" s="17" t="s">
+    </row>
+    <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C20" s="16" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C20" s="18" t="s">
+    <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C21" s="15" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="C21" s="17" t="s">
+    <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="2" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="3" t="s">
+      <c r="C22" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="C22" s="18" t="s">
+    </row>
+    <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="14" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="16" t="s">
+      <c r="C23" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="C23" s="17" t="s">
+    </row>
+    <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="2" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="3" t="s">
+      <c r="C24" s="16" t="s">
         <v>108</v>
-      </c>
-      <c r="C24" s="18" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="19" t="s">
+      <c r="B26" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="C26" s="17"/>
+    </row>
+    <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B27" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C27" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="C26" s="19"/>
-    </row>
-    <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="C27" s="17" t="s">
+    </row>
+    <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B28" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C28" s="16" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C28" s="18" t="s">
+    <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B29" s="14" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="16" t="s">
+      <c r="C29" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="C29" s="17" t="s">
+    </row>
+    <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B30" s="2" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="3" t="s">
+      <c r="C30" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="C30" s="18" t="s">
+    </row>
+    <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B31" s="14" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="16" t="s">
+      <c r="C31" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="C31" s="17" t="s">
+    </row>
+    <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B32" s="2" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="3" t="s">
+      <c r="C32" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="C32" s="18" t="s">
+    </row>
+    <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B33" s="14" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="16" t="s">
+      <c r="C33" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="C33" s="17" t="s">
+    </row>
+    <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B34" s="2" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="3" t="s">
+      <c r="C34" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="C34" s="18" t="s">
+    </row>
+    <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B35" s="14" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="16" t="s">
+      <c r="C35" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="C35" s="17" t="s">
+    </row>
+    <row r="36" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B36" s="2" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="36" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="3" t="s">
+      <c r="C36" s="16" t="s">
         <v>127</v>
-      </c>
-      <c r="C36" s="18" t="s">
-        <v>128</v>
       </c>
     </row>
   </sheetData>
